--- a/static/excel/TGT_model.xlsx
+++ b/static/excel/TGT_model.xlsx
@@ -7809,16 +7809,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8191,10 +8191,10 @@
         <v>-0.0002</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.0354</v>
+        <v>0.0369</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.0294</v>
+        <v>0.0296</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8566,10 +8566,10 @@
         <v>104762</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>108466.1</v>
+        <v>108630.5</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>111659.5</v>
+        <v>111847.9</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8606,27 +8606,27 @@
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>107,111 — 110,388</t>
+          <t>106,262 — 109,514</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>108,619 — 114,335</t>
+          <t>107,659 — 113,405</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>115,209 — 115,525</t>
+          <t>115,318 — 115,850</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>116,151 — 121,362</t>
+          <t>115,962 — 120,413</t>
         </is>
       </c>
       <c r="L16" s="82" t="inlineStr">
         <is>
-          <t>119,958 — 125,341</t>
+          <t>119,763 — 124,360</t>
         </is>
       </c>
       <c r="M16" s="83" t="inlineStr">
@@ -8650,10 +8650,10 @@
         <v>23</v>
       </c>
       <c r="H17" s="84" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" s="84" t="n">
         <v>27</v>
-      </c>
-      <c r="I17" s="84" t="n">
-        <v>25</v>
       </c>
       <c r="J17" s="84" t="n">
         <v>17</v>
@@ -8781,10 +8781,10 @@
         <v>8606.4</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>8910.700000000001</v>
+        <v>8924.200000000001</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>9173.1</v>
+        <v>9188.6</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8821,27 +8821,27 @@
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>8,799 — 9,069</t>
+          <t>8,730 — 8,997</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>8,923 — 9,393</t>
+          <t>8,844 — 9,316</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>9,465 — 9,491</t>
+          <t>9,474 — 9,517</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>9,542 — 9,970</t>
+          <t>9,527 — 9,892</t>
         </is>
       </c>
       <c r="L21" s="82" t="inlineStr">
         <is>
-          <t>9,855 — 10,297</t>
+          <t>9,839 — 10,216</t>
         </is>
       </c>
       <c r="M21" s="83" t="inlineStr">
@@ -10197,7 +10197,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TGT  |  Master Prompt v2  |  23 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — TGT  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 12.9x  |  5yr avg 17.6x  |  DCF-implied 12.4x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=12.0 → blended 40/40/20=10.40]</t>
+          <t>Current 12.9x  |  5yr avg 17.6x  |  DCF-implied 11.2x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | fwd_pe=15.1x→9.13 | abs=12.0 → blended 40/40/20=10.05]  PEG=707.63 (fwd_pe=15.1x / eps_growth=2%)</t>
         </is>
       </c>
       <c r="E22" s="135" t="inlineStr">
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>10.4</v>
+        <v>10.05</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 12.9x  |  5yr avg 17.6x  |  DCF-implied 12.4x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=12.0 → blended 40/40/20=10.40]</t>
+          <t>Current 12.9x  |  5yr avg 17.6x  |  DCF-implied 11.2x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | fwd_pe=15.1x→9.13 | abs=12.0 → blended 40/40/20=10.05]  PEG=707.63 (fwd_pe=15.1x / eps_growth=2%)</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 16.9x  |  5yr avg 17.4x  |  DCF-implied 16.2x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.43 | no_fwd_data(fallback) | abs=10.0 → blended 40/40/20=7.94]</t>
+          <t>Current 16.9x  |  5yr avg 17.4x  |  DCF-implied 14.7x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.43 | fwd_pfcf=19.4x→5.16 | abs=10.0 → blended 40/40/20=7.04]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>7.94</v>
+        <v>7.04</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 16.9x  |  5yr avg 17.4x  |  DCF-implied 16.2x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.43 | no_fwd_data(fallback) | abs=10.0 → blended 40/40/20=7.94]</t>
+          <t>Current 16.9x  |  5yr avg 17.4x  |  DCF-implied 14.7x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.43 | fwd_pfcf=19.4x→5.16 | abs=10.0 → blended 40/40/20=7.04]</t>
         </is>
       </c>
     </row>

--- a/static/excel/TGT_model.xlsx
+++ b/static/excel/TGT_model.xlsx
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7653,25 +7653,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7714,11 +7716,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0529</v>
+        <v>0.05279999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.72%</t>
+          <t>Rf 4.56% + spread 0.72%</t>
         </is>
       </c>
     </row>
@@ -7744,11 +7746,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0409</v>
+        <v>0.0441</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -8621,12 +8623,12 @@
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>115,962 — 120,413</t>
+          <t>115,907 — 120,407</t>
         </is>
       </c>
       <c r="L16" s="82" t="inlineStr">
         <is>
-          <t>119,763 — 124,360</t>
+          <t>119,707 — 124,354</t>
         </is>
       </c>
       <c r="M16" s="83" t="inlineStr">
@@ -8650,7 +8652,7 @@
         <v>23</v>
       </c>
       <c r="H17" s="84" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="84" t="n">
         <v>27</v>
@@ -8836,12 +8838,12 @@
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>9,527 — 9,892</t>
+          <t>9,522 — 9,892</t>
         </is>
       </c>
       <c r="L21" s="82" t="inlineStr">
         <is>
-          <t>9,839 — 10,216</t>
+          <t>9,834 — 10,216</t>
         </is>
       </c>
       <c r="M21" s="83" t="inlineStr">
@@ -10197,7 +10199,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TGT  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — TGT  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10714,16 +10716,16 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 12.9x  |  5yr avg 17.6x  |  DCF-implied 11.2x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | fwd_pe=15.1x→9.13 | abs=12.0 → blended 40/40/20=10.05]  PEG=707.63 (fwd_pe=15.1x / eps_growth=2%)</t>
-        </is>
-      </c>
-      <c r="E22" s="135" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Fwd P/E 15.1x (scoring basis)  |  5yr avg 16.7x  |  DCF-implied 11.2x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.44 | fwd_pe=15.1x→8.44 | abs=10.0 → blended 40/40/20=8.75]  PEG=707.63 (fwd_pe=15.1x / eps_growth=2%)</t>
+        </is>
+      </c>
+      <c r="E22" s="137" t="inlineStr">
+        <is>
+          <t>MOD-HIGH</t>
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>10.05</v>
+        <v>8.75</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10731,7 +10733,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 12.9x  |  5yr avg 17.6x  |  DCF-implied 11.2x [ref only — not used as benchmark]  [-27% vs benchmark]  [trail=10.00 | fwd_pe=15.1x→9.13 | abs=12.0 → blended 40/40/20=10.05]  PEG=707.63 (fwd_pe=15.1x / eps_growth=2%)</t>
+          <t>Fwd P/E 15.1x (scoring basis)  |  5yr avg 16.7x  |  DCF-implied 11.2x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.44 | fwd_pe=15.1x→8.44 | abs=10.0 → blended 40/40/20=8.75]  PEG=707.63 (fwd_pe=15.1x / eps_growth=2%)</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10753,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 16.9x  |  5yr avg 17.4x  |  DCF-implied 14.7x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.43 | fwd_pfcf=19.4x→5.16 | abs=10.0 → blended 40/40/20=7.04]</t>
+          <t>Current 16.9x  |  5yr avg 17.3x  |  DCF-implied 14.7x [ref only — not used as benchmark]  [-2% vs benchmark]  [trail=7.35 | fwd_pfcf=19.4x→5.06 | abs=10.0 → blended 40/40/20=6.96]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10760,7 +10762,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>7.04</v>
+        <v>6.96</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10768,7 +10770,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 16.9x  |  5yr avg 17.4x  |  DCF-implied 14.7x [ref only — not used as benchmark]  [-3% vs benchmark]  [trail=7.43 | fwd_pfcf=19.4x→5.16 | abs=10.0 → blended 40/40/20=7.04]</t>
+          <t>Current 16.9x  |  5yr avg 17.3x  |  DCF-implied 14.7x [ref only — not used as benchmark]  [-2% vs benchmark]  [trail=7.35 | fwd_pfcf=19.4x→5.06 | abs=10.0 → blended 40/40/20=6.96]</t>
         </is>
       </c>
     </row>
